--- a/submission_packages/frontiers_signal_processing_20260601/05_supplementary_files/Supplementary_Tables_CTGFHT.xlsx
+++ b/submission_packages/frontiers_signal_processing_20260601/05_supplementary_files/Supplementary_Tables_CTGFHT.xlsx
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pipeline scripts are named and the versioned repository archive is available at https://doi.org/10.5281/zenodo.20376424.</t>
+          <t>Pipeline scripts are named and the versioned repository archive is available at https://doi.org/10.5281/zenodo.20484443.</t>
         </is>
       </c>
     </row>

--- a/submission_packages/frontiers_signal_processing_20260601/05_supplementary_files/Supplementary_Tables_CTGFHT.xlsx
+++ b/submission_packages/frontiers_signal_processing_20260601/05_supplementary_files/Supplementary_Tables_CTGFHT.xlsx
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pipeline scripts are named and the versioned repository archive is available at https://doi.org/10.5281/zenodo.20484443.</t>
+          <t>Pipeline scripts are named and the versioned repository archive is available at https://doi.org/10.5281/zenodo.20485068.</t>
         </is>
       </c>
     </row>
